--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484289_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484289_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7552</v>
+        <v>3.3407</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0103</v>
+        <v>3.6775</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2552</v>
+        <v>-0.3369</v>
       </c>
       <c r="G2" t="n">
         <v>1.6499</v>
@@ -610,13 +610,13 @@
         <v>1.1721</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6213</v>
+        <v>-0.0358</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.1196</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1655</v>
+        <v>0.0838</v>
       </c>
       <c r="V2" t="n">
         <v>0.5545</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9545</v>
+        <v>1.5973</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2975</v>
+        <v>0.7714</v>
       </c>
       <c r="F3" t="n">
-        <v>0.657</v>
+        <v>0.8259</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0466</v>
+        <v>0.039</v>
       </c>
       <c r="H3" t="n">
-        <v>0.779</v>
+        <v>-2.0791</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2677</v>
+        <v>2.118</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9177</v>
+        <v>1.012</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1893</v>
+        <v>-0.8366</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7284</v>
+        <v>1.8486</v>
       </c>
       <c r="M3" t="n">
-        <v>1.129</v>
+        <v>-0.9731</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5897</v>
+        <v>-1.2425</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5393</v>
+        <v>0.2694</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5991</v>
+        <v>-0.2779</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3565</v>
+        <v>-0.2406</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2425</v>
+        <v>-0.0373</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4959</v>
+        <v>0.6642</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4959</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0748</v>
+        <v>0.986</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.3731</v>
+        <v>-0.7266</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4479</v>
+        <v>1.7126</v>
       </c>
       <c r="G4" t="n">
         <v>-0.06519999999999999</v>
@@ -766,13 +766,13 @@
         <v>3.1255</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3446</v>
+        <v>-0.4334</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.6066</v>
+        <v>-0.96</v>
       </c>
       <c r="U4" t="n">
-        <v>1.262</v>
+        <v>0.5266</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6642</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9634</v>
+        <v>0.6443</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1647</v>
+        <v>0.2052</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7987</v>
+        <v>0.4391</v>
       </c>
       <c r="G5" t="n">
-        <v>0.039</v>
+        <v>2.0466</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.0791</v>
+        <v>0.779</v>
       </c>
       <c r="I5" t="n">
-        <v>2.118</v>
+        <v>1.2677</v>
       </c>
       <c r="J5" t="n">
-        <v>1.012</v>
+        <v>0.9177</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8366</v>
+        <v>0.1893</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8486</v>
+        <v>0.7284</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9731</v>
+        <v>1.129</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2425</v>
+        <v>0.5897</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2694</v>
+        <v>0.5393</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9118000000000001</v>
+        <v>0.2888</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8473000000000001</v>
+        <v>0.2642</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0645</v>
+        <v>0.0246</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6642</v>
+        <v>-1.4959</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6642</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7209</v>
+        <v>-1.1147</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3531</v>
+        <v>-2.5305</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3678</v>
+        <v>1.4157</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7615</v>
+        <v>-0.9165</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0714</v>
+        <v>-0.1348</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3099</v>
+        <v>-0.7817</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6119</v>
+        <v>-0.3331</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6524</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>-1.3206</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1496</v>
+        <v>-0.5834</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.419</v>
+        <v>-1.1223</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2694</v>
+        <v>0.5389</v>
       </c>
       <c r="P6" t="n">
         <v>0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5627</v>
+        <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9504</v>
+        <v>-1.1163</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2355</v>
+        <v>-0.7984</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2851</v>
+        <v>-0.318</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4959</v>
+        <v>0.3321</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4959</v>
+        <v>-0.2224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1733</v>
+        <v>-1.5626</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.9534</v>
+        <v>-1.3037</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7801</v>
+        <v>-0.2588</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.7615</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4201</v>
+        <v>-1.0714</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0385</v>
+        <v>0.3099</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.6122</v>
+        <v>-0.6119</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3044</v>
+        <v>-0.6524</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3077</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9938</v>
+        <v>-0.1496</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7245</v>
+        <v>-0.419</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2692</v>
+        <v>0.2694</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1409</v>
+        <v>0.1087</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3878</v>
+        <v>0.2849</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2469</v>
+        <v>-0.1761</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2483</v>
+        <v>-1.6255</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.3395</v>
+        <v>-4.0162</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0912</v>
+        <v>2.3907</v>
       </c>
       <c r="G8" t="n">
         <v>-1.4232</v>
@@ -1078,13 +1078,13 @@
         <v>3.3208</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6381</v>
+        <v>-1.0152</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8719</v>
+        <v>-0.5487</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7661</v>
+        <v>-0.4666</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5545</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3193</v>
+        <v>-2.4252</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2176</v>
+        <v>-4.0146</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8983</v>
+        <v>1.5895</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9165</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1348</v>
+        <v>0.4201</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7817</v>
+        <v>-1.0385</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3331</v>
+        <v>-1.6122</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9874000000000001</v>
+        <v>-0.3044</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3206</v>
+        <v>-1.3077</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5834</v>
+        <v>0.9938</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1223</v>
+        <v>0.7245</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5389</v>
+        <v>0.2692</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5395</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.3209</v>
+        <v>-0.3928</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4855</v>
+        <v>-0.449</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8354</v>
+        <v>0.0562</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3321</v>
+        <v>-1.2186</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2224</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1438</v>
+        <v>-2.8048</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.693</v>
+        <v>-3.572</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5493</v>
+        <v>0.7672</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2601</v>
@@ -1234,13 +1234,13 @@
         <v>2.1488</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.079</v>
+        <v>-0.74</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3878</v>
+        <v>-0.2667</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6912</v>
+        <v>-0.4733</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9739</v>
+        <v>-5.6567</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8426</v>
+        <v>-4.5799</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1313</v>
+        <v>-1.0768</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4568</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6102</v>
+        <v>-0.293</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3026</v>
+        <v>-0.0399</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3076</v>
+        <v>-0.2532</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.831600000000002</v>
+        <v>-8.6212</v>
       </c>
       <c r="E12" t="n">
-        <v>-17.2998</v>
+        <v>-16.0894</v>
       </c>
       <c r="F12" t="n">
-        <v>7.468200000000001</v>
+        <v>7.4682</v>
       </c>
       <c r="G12" t="n">
         <v>-3.7662</v>
@@ -1360,7 +1360,7 @@
         <v>-5.116400000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>1.350100000000001</v>
+        <v>1.3501</v>
       </c>
       <c r="J12" t="n">
         <v>-0.4505999999999992</v>
@@ -1390,16 +1390,16 @@
         <v>17.581</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.117299999999999</v>
+        <v>-3.9069</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.0843</v>
+        <v>-2.8738</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.033</v>
+        <v>-1.0333</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.8783</v>
+        <v>-3.878299999999999</v>
       </c>
       <c r="W12" t="n">
         <v>1.8858</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4778</v>
+        <v>3.6657</v>
       </c>
       <c r="E13" t="n">
         <v>-0.0083</v>
       </c>
       <c r="F13" t="n">
-        <v>3.486</v>
+        <v>3.674</v>
       </c>
       <c r="G13" t="n">
         <v>1.4148</v>
@@ -1468,13 +1468,13 @@
         <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6994</v>
+        <v>0.8873</v>
       </c>
       <c r="T13" t="n">
         <v>-0.0246</v>
       </c>
       <c r="U13" t="n">
-        <v>0.724</v>
+        <v>0.9119</v>
       </c>
       <c r="V13" t="n">
         <v>0.3869</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8227</v>
+        <v>3.3024</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.7604</v>
+        <v>-1.6593</v>
       </c>
       <c r="F14" t="n">
-        <v>4.5831</v>
+        <v>4.9617</v>
       </c>
       <c r="G14" t="n">
         <v>1.7227</v>
@@ -1546,13 +1546,13 @@
         <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4358</v>
+        <v>0.9155</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1457</v>
+        <v>-0.0446</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5814</v>
+        <v>0.96</v>
       </c>
       <c r="V14" t="n">
         <v>0.6642</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>P. GONZÁLEZ BRUMOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1536</v>
+        <v>2.0046</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5656</v>
+        <v>1.4152</v>
       </c>
       <c r="F15" t="n">
-        <v>0.588</v>
+        <v>0.5894</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.768</v>
+        <v>2.0957</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5405</v>
+        <v>3.9031</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3085</v>
+        <v>-1.8073</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4753</v>
+        <v>3.1392</v>
       </c>
       <c r="K15" t="n">
-        <v>1.109</v>
+        <v>4.4065</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.2673</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2433</v>
+        <v>-1.0435</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5684</v>
+        <v>-0.5034</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.5401</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1485</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1888</v>
+        <v>0.2925</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0403</v>
+        <v>0.5074</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7731</v>
+        <v>-0.1097</v>
       </c>
       <c r="W15" t="n">
-        <v>2.0503</v>
+        <v>1.1089</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0785</v>
+        <v>1.792</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5163</v>
+        <v>0.9589</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5622</v>
+        <v>0.8331</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0957</v>
+        <v>-0.768</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9031</v>
+        <v>0.5405</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8073</v>
+        <v>-1.3085</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1392</v>
+        <v>0.4753</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4065</v>
+        <v>1.109</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2673</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0435</v>
+        <v>-1.2433</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5034</v>
+        <v>-0.5684</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5401</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1255</v>
+        <v>-2.1488</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3441</v>
+        <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8738</v>
+        <v>0.7869</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3936</v>
+        <v>0.5821</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4802</v>
+        <v>0.2048</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1097</v>
+        <v>1.7731</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1089</v>
+        <v>2.0503</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1306</v>
+        <v>1.2474</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4838</v>
+        <v>-0.585</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6145</v>
+        <v>1.8324</v>
       </c>
       <c r="G17" t="n">
         <v>1.0926</v>
@@ -1780,13 +1780,13 @@
         <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4287</v>
+        <v>0.5454</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3247</v>
+        <v>0.2236</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1039</v>
+        <v>0.3218</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5787</v>
+        <v>0.4476</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.1152</v>
+        <v>-3.2163</v>
       </c>
       <c r="F18" t="n">
-        <v>3.6939</v>
+        <v>3.664</v>
       </c>
       <c r="G18" t="n">
         <v>1.2304</v>
@@ -1858,13 +1858,13 @@
         <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2198</v>
+        <v>1.0888</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0359</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1839</v>
+        <v>1.154</v>
       </c>
       <c r="V18" t="n">
         <v>0.2772</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5787</v>
+        <v>0.2168</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3694</v>
+        <v>-0.2683</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.4851</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5007</v>
@@ -1936,13 +1936,13 @@
         <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7202</v>
+        <v>0.3583</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0221</v>
+        <v>0.1232</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.2351</v>
       </c>
       <c r="V19" t="n">
         <v>0.5545</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7423</v>
+        <v>0.1166</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8534</v>
+        <v>0.408</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1111</v>
+        <v>-0.2914</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8489</v>
+        <v>-0.8594000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4853</v>
+        <v>0.1384</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3636</v>
+        <v>-0.9978</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9728</v>
+        <v>0.379</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5308</v>
+        <v>0.4323</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.442</v>
+        <v>-0.0533</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1239</v>
+        <v>-1.2384</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0456</v>
+        <v>-0.2939</v>
       </c>
       <c r="O20" t="n">
-        <v>1.0784</v>
+        <v>-0.9445</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.9301</v>
+        <v>1.1721</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1539</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.589</v>
+        <v>0.029</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5649</v>
+        <v>0.0522</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8828</v>
+        <v>-0.2772</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9776</v>
+        <v>-0.7088</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1987</v>
+        <v>-1.2553</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.779</v>
+        <v>0.5464</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8594000000000001</v>
+        <v>-0.8131</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1384</v>
+        <v>-0.1384</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9978</v>
+        <v>-0.6747</v>
       </c>
       <c r="J21" t="n">
-        <v>0.379</v>
+        <v>-0.3236</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4323</v>
+        <v>0.3505</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0533</v>
+        <v>-0.6741</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2384</v>
+        <v>-0.4895</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2939</v>
+        <v>-0.4889</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9445</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.013</v>
+        <v>0.0103</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5777</v>
+        <v>-0.2674</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4353</v>
+        <v>0.2778</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2772</v>
+        <v>-1.2735</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2689</v>
+        <v>-0.9044</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7608</v>
+        <v>-3.2579</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4919</v>
+        <v>2.3535</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8131</v>
+        <v>-0.8489</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1384</v>
+        <v>-0.4853</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6747</v>
+        <v>-0.3636</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3236</v>
+        <v>-1.9728</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3505</v>
+        <v>-0.5308</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6741</v>
+        <v>-1.442</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4895</v>
+        <v>1.1239</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4889</v>
+        <v>0.0456</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>1.0784</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3674</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5497</v>
+        <v>0.9918</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.773</v>
+        <v>0.1845</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2233</v>
+        <v>0.8074</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2735</v>
+        <v>1.8828</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>2.4373</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6093</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>9.831799999999998</v>
+        <v>11.1799</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.4681</v>
+        <v>-7.468299999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>17.2998</v>
+        <v>18.6482</v>
       </c>
       <c r="G23" t="n">
         <v>3.7661</v>
@@ -2233,13 +2233,13 @@
         <v>0.4505999999999997</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8925000000000001</v>
+        <v>-0.8925</v>
       </c>
       <c r="O23" t="n">
         <v>1.3433</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.930099999999999</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q23" t="n">
         <v>-17.581</v>
@@ -2248,13 +2248,13 @@
         <v>14.6508</v>
       </c>
       <c r="S23" t="n">
-        <v>5.1174</v>
+        <v>6.465400000000001</v>
       </c>
       <c r="T23" t="n">
         <v>1.0331</v>
       </c>
       <c r="U23" t="n">
-        <v>4.0841</v>
+        <v>5.432400000000001</v>
       </c>
       <c r="V23" t="n">
         <v>3.8783</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484289_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484289_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.986</v>
+        <v>1.5279</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7266</v>
+        <v>1.5279</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7126</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.06519999999999999</v>
+        <v>1.5279</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5285</v>
+        <v>0.921</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5938</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9878</v>
+        <v>1.5279</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5809</v>
+        <v>0.921</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.053</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0524</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1255</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4334</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.96</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5266</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6443</v>
+        <v>0.986</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2052</v>
+        <v>-0.7266</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4391</v>
+        <v>1.7126</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0466</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.779</v>
+        <v>0.5285</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2677</v>
+        <v>-0.5938</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9177</v>
+        <v>0.9878</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1893</v>
+        <v>1.5809</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7284</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>1.129</v>
+        <v>-1.053</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5897</v>
+        <v>-1.0524</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5393</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1953</v>
+        <v>2.1488</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7814</v>
+        <v>3.1255</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2888</v>
+        <v>-0.4334</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2642</v>
+        <v>-0.96</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0246</v>
+        <v>0.5266</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4959</v>
+        <v>-0.6642</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2224</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4959</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1147</v>
+        <v>0.6443</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.5305</v>
+        <v>0.2052</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4157</v>
+        <v>0.4391</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9165</v>
+        <v>2.0466</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1348</v>
+        <v>0.779</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7817</v>
+        <v>1.2677</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3331</v>
+        <v>0.9177</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.1893</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3206</v>
+        <v>0.7284</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5834</v>
+        <v>1.129</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1223</v>
+        <v>0.5897</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5389</v>
+        <v>0.5393</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1163</v>
+        <v>0.2888</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7984</v>
+        <v>0.2642</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.318</v>
+        <v>0.0246</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3321</v>
+        <v>-1.4959</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2224</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5626</v>
+        <v>-1.1147</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3037</v>
+        <v>-2.5305</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2588</v>
+        <v>1.4157</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7615</v>
+        <v>-0.9165</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0714</v>
+        <v>-0.1348</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3099</v>
+        <v>-0.7817</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6119</v>
+        <v>-0.3331</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6524</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>-1.3206</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1496</v>
+        <v>-0.5834</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.419</v>
+        <v>-1.1223</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2694</v>
+        <v>0.5389</v>
       </c>
       <c r="P7" t="n">
         <v>0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5627</v>
+        <v>2.5395</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1087</v>
+        <v>-1.1163</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2849</v>
+        <v>-0.7984</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1761</v>
+        <v>-0.318</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4959</v>
+        <v>0.3321</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4959</v>
+        <v>-0.2224</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1068,72 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6255</v>
+        <v>-1.5626</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.0162</v>
+        <v>-1.3037</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3907</v>
+        <v>-0.2588</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4232</v>
+        <v>-0.7615</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6265</v>
+        <v>-1.0714</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2033</v>
+        <v>0.3099</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5141</v>
+        <v>-0.6119</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7739</v>
+        <v>-0.6524</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7402</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>0.09089999999999999</v>
+        <v>-0.1496</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8526</v>
+        <v>-0.419</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9435</v>
+        <v>0.2694</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>3.3208</v>
+        <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0152</v>
+        <v>0.1087</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5487</v>
+        <v>0.2849</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4666</v>
+        <v>-0.1761</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5545</v>
+        <v>-1.4959</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5545</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,11 +1296,16 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6567</v>
+        <v>-3.1534</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5799</v>
+        <v>-5.5442</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0768</v>
+        <v>2.3907</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4568</v>
+        <v>-2.9511</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5129</v>
+        <v>-2.5475</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9439</v>
+        <v>-0.4037</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6332</v>
+        <v>-3.0421</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0409</v>
+        <v>-1.6948</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6741</v>
+        <v>-1.3472</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8237</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5538</v>
+        <v>-0.8526</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2698</v>
+        <v>0.9435</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.9069</v>
+        <v>1.3674</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.3208</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.293</v>
+        <v>-1.0152</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0399</v>
+        <v>-0.5487</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2532</v>
+        <v>-0.4666</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,926 +1400,1227 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.6212</v>
+        <v>-5.6567</v>
       </c>
       <c r="E12" t="n">
-        <v>-16.0894</v>
+        <v>-4.5799</v>
       </c>
       <c r="F12" t="n">
-        <v>7.4682</v>
+        <v>-1.0768</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7662</v>
+        <v>-1.4568</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.116400000000001</v>
+        <v>-0.5129</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3501</v>
+        <v>-0.9439</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4505999999999992</v>
+        <v>-0.6332</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8924</v>
+        <v>0.0409</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3432</v>
+        <v>-0.6741</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.3156</v>
+        <v>-0.8237</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.0089</v>
+        <v>-0.5538</v>
       </c>
       <c r="O12" t="n">
-        <v>2.6934</v>
+        <v>-0.2698</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9302</v>
+        <v>-3.9069</v>
       </c>
       <c r="Q12" t="n">
-        <v>-14.6506</v>
+        <v>-3.9069</v>
       </c>
       <c r="R12" t="n">
-        <v>17.581</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.9069</v>
+        <v>-0.293</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.8738</v>
+        <v>-0.0399</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0333</v>
+        <v>-0.2532</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.878299999999999</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8858</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.764099999999999</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6657</v>
+        <v>-8.6212</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0083</v>
+        <v>-16.0895</v>
       </c>
       <c r="F13" t="n">
-        <v>3.674</v>
+        <v>7.4682</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4148</v>
+        <v>-3.7662</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3515</v>
+        <v>-5.116400000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7663</v>
+        <v>1.3501</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0164</v>
+        <v>-0.4507000000000003</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6716</v>
+        <v>0.8925000000000002</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6879</v>
+        <v>-1.3432</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3984</v>
+        <v>-3.3156</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3201</v>
+        <v>-6.0089</v>
       </c>
       <c r="O13" t="n">
-        <v>1.0784</v>
+        <v>2.6934</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9767</v>
+        <v>2.9302</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-14.6506</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9767</v>
+        <v>17.581</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8873</v>
+        <v>-3.9069</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0246</v>
+        <v>-2.8738</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9119</v>
+        <v>-1.0333</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3869</v>
+        <v>-3.8783</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.8858</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3869</v>
-      </c>
+        <v>-5.7641</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3024</v>
+        <v>3.6657</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6593</v>
+        <v>-0.0083</v>
       </c>
       <c r="F14" t="n">
-        <v>4.9617</v>
+        <v>3.674</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7227</v>
+        <v>1.4148</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1852</v>
+        <v>-0.3515</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5375</v>
+        <v>1.7663</v>
       </c>
       <c r="J14" t="n">
-        <v>0.534</v>
+        <v>0.0164</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0601</v>
+        <v>-0.6716</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5942</v>
+        <v>0.6879</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1887</v>
+        <v>1.3984</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2454</v>
+        <v>0.3201</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9433</v>
+        <v>1.0784</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9155</v>
+        <v>0.8873</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0446</v>
+        <v>-0.0246</v>
       </c>
       <c r="U14" t="n">
-        <v>0.96</v>
+        <v>0.9119</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6642</v>
+        <v>0.3869</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6642</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0046</v>
+        <v>2.9954</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4152</v>
+        <v>-1.9663</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5894</v>
+        <v>4.9617</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0957</v>
+        <v>1.4158</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9031</v>
+        <v>-0.1217</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8073</v>
+        <v>1.5375</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1392</v>
+        <v>0.227</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4065</v>
+        <v>-0.3671</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2673</v>
+        <v>0.5942</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0435</v>
+        <v>1.1887</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5034</v>
+        <v>0.2454</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5401</v>
+        <v>0.9433</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.1255</v>
+        <v>-2.1488</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3441</v>
+        <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.9155</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2925</v>
+        <v>-0.0446</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5074</v>
+        <v>0.96</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1097</v>
+        <v>0.6642</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>P. GONZALEZ BRUMOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.792</v>
+        <v>2.0046</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9589</v>
+        <v>1.4152</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8331</v>
+        <v>0.5894</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.768</v>
+        <v>2.0957</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5405</v>
+        <v>3.9031</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3085</v>
+        <v>-1.8073</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4753</v>
+        <v>3.1392</v>
       </c>
       <c r="K16" t="n">
-        <v>1.109</v>
+        <v>4.4065</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.2673</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2433</v>
+        <v>-1.0435</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5684</v>
+        <v>-0.5034</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.5401</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7869</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5821</v>
+        <v>0.2925</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2048</v>
+        <v>0.5074</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7731</v>
+        <v>-0.1097</v>
       </c>
       <c r="W16" t="n">
-        <v>2.0503</v>
+        <v>1.1089</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2474</v>
+        <v>1.792</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.585</v>
+        <v>0.9589</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8324</v>
+        <v>0.8331</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0926</v>
+        <v>-0.768</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1758</v>
+        <v>0.5405</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9169</v>
+        <v>-1.3085</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3635</v>
+        <v>0.4753</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.284</v>
+        <v>1.109</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6475</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7292</v>
+        <v>-1.2433</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4597</v>
+        <v>-0.5684</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2694</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5454</v>
+        <v>0.7869</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2236</v>
+        <v>0.5821</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3218</v>
+        <v>0.2048</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.7731</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.0503</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4476</v>
+        <v>1.2474</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.2163</v>
+        <v>-0.585</v>
       </c>
       <c r="F18" t="n">
-        <v>3.664</v>
+        <v>1.8324</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2304</v>
+        <v>1.0926</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0711</v>
+        <v>0.1758</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1593</v>
+        <v>0.9169</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3028</v>
+        <v>0.3635</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3838</v>
+        <v>-0.284</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>0.6475</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5332</v>
+        <v>0.7292</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4549</v>
+        <v>0.4597</v>
       </c>
       <c r="O18" t="n">
-        <v>1.0784</v>
+        <v>0.2694</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1488</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1255</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0888</v>
+        <v>0.5454</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.2236</v>
       </c>
       <c r="U18" t="n">
-        <v>1.154</v>
+        <v>0.3218</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2168</v>
+        <v>0.4476</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2683</v>
+        <v>-3.2163</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4851</v>
+        <v>3.664</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5007</v>
+        <v>1.2304</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0775</v>
+        <v>0.0711</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5782</v>
+        <v>1.1593</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0074</v>
+        <v>-0.3028</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6411</v>
+        <v>-0.3838</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0809</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5081</v>
+        <v>1.5332</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5636</v>
+        <v>0.4549</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9445</v>
+        <v>1.0784</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-3.1255</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3583</v>
+        <v>1.0888</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1232</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2351</v>
+        <v>1.154</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5545</v>
+        <v>0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5545</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1166</v>
+        <v>0.307</v>
       </c>
       <c r="E20" t="n">
-        <v>0.408</v>
+        <v>0.307</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2914</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8594000000000001</v>
+        <v>0.307</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1384</v>
+        <v>0.307</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9978</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.379</v>
+        <v>0.307</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4323</v>
+        <v>0.307</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0533</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2384</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2939</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9445</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.08119999999999999</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0522</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7088</v>
+        <v>0.307</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2553</v>
+        <v>0.307</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5464</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8131</v>
+        <v>0.307</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1384</v>
+        <v>0.307</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6747</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3236</v>
+        <v>0.307</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3505</v>
+        <v>0.307</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4895</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4889</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0103</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2674</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2778</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2735</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9044</v>
+        <v>0.2168</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2579</v>
+        <v>-0.2683</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3535</v>
+        <v>0.4851</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8489</v>
+        <v>-0.5007</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4853</v>
+        <v>1.0775</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3636</v>
+        <v>-1.5782</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.9728</v>
+        <v>1.0074</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5308</v>
+        <v>1.6411</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.442</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1239</v>
+        <v>-1.5081</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0456</v>
+        <v>-0.5636</v>
       </c>
       <c r="O22" t="n">
-        <v>1.0784</v>
+        <v>-0.9445</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9918</v>
+        <v>0.3583</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1845</v>
+        <v>0.1232</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8074</v>
+        <v>0.2351</v>
       </c>
       <c r="V22" t="n">
-        <v>1.8828</v>
+        <v>0.5545</v>
       </c>
       <c r="W22" t="n">
-        <v>2.4373</v>
+        <v>0.5545</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>0.1166</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.2914</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.8594000000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1384</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.9978</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.4323</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.0533</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.2384</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.2939</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.9445</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.08119999999999999</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>R. FERNANDEZ DIAZ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.9044</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.2579</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.3535</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.8489</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.4853</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.3636</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.9728</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.5308</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.442</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.1239</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.0784</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.9918</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.8074</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.8828</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.4373</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>E. MARTIN GASCON</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1.0158</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.5622</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.5464</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.1201</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.4454</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.6747</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.6306</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.4895</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.4889</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.0103</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.2674</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.2735</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484289_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>11.1799</v>
       </c>
-      <c r="E23" t="n">
-        <v>-7.468299999999999</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="E26" t="n">
+        <v>-7.4682</v>
+      </c>
+      <c r="F26" t="n">
         <v>18.6482</v>
       </c>
-      <c r="G23" t="n">
-        <v>3.7661</v>
-      </c>
-      <c r="H23" t="n">
-        <v>5.116400000000001</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="G26" t="n">
+        <v>3.7662</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.1165</v>
+      </c>
+      <c r="I26" t="n">
         <v>-1.3501</v>
       </c>
-      <c r="J23" t="n">
-        <v>3.3156</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="J26" t="n">
+        <v>3.315599999999998</v>
+      </c>
+      <c r="K26" t="n">
         <v>6.0091</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L26" t="n">
         <v>-2.6934</v>
       </c>
-      <c r="M23" t="n">
-        <v>0.4505999999999997</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="M26" t="n">
+        <v>0.4505999999999999</v>
+      </c>
+      <c r="N26" t="n">
         <v>-0.8925</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O26" t="n">
         <v>1.3433</v>
       </c>
-      <c r="P23" t="n">
-        <v>-2.9301</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="P26" t="n">
+        <v>-2.930099999999999</v>
+      </c>
+      <c r="Q26" t="n">
         <v>-17.581</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R26" t="n">
         <v>14.6508</v>
       </c>
-      <c r="S23" t="n">
-        <v>6.465400000000001</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="S26" t="n">
+        <v>6.4654</v>
+      </c>
+      <c r="T26" t="n">
         <v>1.0331</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U26" t="n">
         <v>5.432400000000001</v>
       </c>
-      <c r="V23" t="n">
-        <v>3.8783</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="V26" t="n">
+        <v>3.878299999999999</v>
+      </c>
+      <c r="W26" t="n">
         <v>5.764</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X26" t="n">
         <v>-1.8857</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
